--- a/sample_data/fifo/FIFO_SAMPLE.xlsx
+++ b/sample_data/fifo/FIFO_SAMPLE.xlsx
@@ -466,21 +466,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46164</v>
+        <v>46207</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30114</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30114</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>L1037</t>
+          <t>L1006</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -494,21 +494,21 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46279</v>
+        <v>46267</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SMP-30112</t>
+          <t>SMP-30101</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sample bracket 30112</t>
+          <t>Sample bracket 30101</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>L1072</t>
+          <t>L1043</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -522,21 +522,21 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46213</v>
+        <v>46286</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SMP-30115</t>
+          <t>SMP-30107</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sample bracket 30115</t>
+          <t>Sample bracket 30107</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>L1036</t>
+          <t>L1068</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -545,26 +545,26 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46284</v>
+        <v>46265</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30104</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30104</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>L1024</t>
+          <t>L1035</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -573,26 +573,26 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46236</v>
+        <v>46205</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMP-30108</t>
+          <t>SMP-30107</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sample bracket 30108</t>
+          <t>Sample bracket 30107</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>L1092</t>
+          <t>L1009</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -601,12 +601,12 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46198</v>
+        <v>46299</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>L1082</t>
+          <t>L1069</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -634,21 +634,21 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46220</v>
+        <v>46192</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30102</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30102</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>L1004</t>
+          <t>L1030</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -657,26 +657,26 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46229</v>
+        <v>46259</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>L1011</t>
+          <t>L1027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -685,26 +685,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46227</v>
+        <v>46288</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SMP-30110</t>
+          <t>SMP-30101</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sample bracket 30110</t>
+          <t>Sample bracket 30101</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>L1022</t>
+          <t>L1000</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -713,26 +713,26 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46221</v>
+        <v>46192</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30108</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30108</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>L1046</t>
+          <t>L1058</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -741,26 +741,26 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46213</v>
+        <v>46234</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SMP-30108</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sample bracket 30108</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>L1032</t>
+          <t>L1093</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -769,26 +769,26 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46227</v>
+        <v>46289</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>L1043</t>
+          <t>L1037</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -797,26 +797,26 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46180</v>
+        <v>46249</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SMP-30114</t>
+          <t>SMP-30101</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sample bracket 30114</t>
+          <t>Sample bracket 30101</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>L1018</t>
+          <t>L1069</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -825,26 +825,26 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46179</v>
+        <v>46298</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SMP-30112</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sample bracket 30112</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>L1071</t>
+          <t>L1074</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -853,26 +853,26 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46220</v>
+        <v>46298</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SMP-30102</t>
+          <t>SMP-30105</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sample bracket 30102</t>
+          <t>Sample bracket 30105</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>L1001</t>
+          <t>L1065</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -881,26 +881,26 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46262</v>
+        <v>46297</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SMP-30103</t>
+          <t>SMP-30105</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sample bracket 30103</t>
+          <t>Sample bracket 30105</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>L1086</t>
+          <t>L1008</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -909,12 +909,12 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46215</v>
+        <v>46292</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>L1047</t>
+          <t>L1072</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -937,26 +937,26 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46260</v>
+        <v>46244</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SMP-30107</t>
+          <t>SMP-30101</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sample bracket 30107</t>
+          <t>Sample bracket 30101</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>L1079</t>
+          <t>L1053</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -970,7 +970,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46195</v>
+        <v>46190</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>L1028</t>
+          <t>L1026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -993,26 +993,26 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46197</v>
+        <v>46280</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SMP-30114</t>
+          <t>SMP-30107</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sample bracket 30114</t>
+          <t>Sample bracket 30107</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>L1038</t>
+          <t>L1016</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1021,26 +1021,26 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46290</v>
+        <v>46275</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SMP-30103</t>
+          <t>SMP-30114</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sample bracket 30103</t>
+          <t>Sample bracket 30114</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>L1004</t>
+          <t>L1096</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1049,26 +1049,26 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46292</v>
+        <v>46262</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SMP-30115</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sample bracket 30115</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>L1030</t>
+          <t>L1072</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1077,26 +1077,26 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>240</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46269</v>
+        <v>46253</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30102</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30102</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>L1047</t>
+          <t>L1064</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1105,26 +1105,26 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46248</v>
+        <v>46190</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30104</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30104</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>L1093</t>
+          <t>L1008</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1138,21 +1138,21 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46239</v>
+        <v>46278</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30111</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30111</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>L1062</t>
+          <t>L1056</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1166,21 +1166,21 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46188</v>
+        <v>46245</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30109</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30109</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>L1035</t>
+          <t>L1083</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1189,26 +1189,26 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>50</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46284</v>
+        <v>46238</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>L1056</t>
+          <t>L1070</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1217,26 +1217,26 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46294</v>
+        <v>46188</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30103</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30103</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>L1087</t>
+          <t>L1017</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1250,21 +1250,21 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46298</v>
+        <v>46201</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30103</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30103</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>L1035</t>
+          <t>L1095</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1273,26 +1273,26 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46185</v>
+        <v>46279</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SMP-30103</t>
+          <t>SMP-30104</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sample bracket 30103</t>
+          <t>Sample bracket 30104</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>L1058</t>
+          <t>L1077</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1301,26 +1301,26 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46241</v>
+        <v>46285</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SMP-30106</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sample bracket 30106</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>L1076</t>
+          <t>L1081</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1329,26 +1329,26 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46221</v>
+        <v>46281</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SMP-30101</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sample bracket 30101</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>L1031</t>
+          <t>L1006</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1357,26 +1357,26 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46297</v>
+        <v>46213</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SMP-30106</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sample bracket 30106</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>L1097</t>
+          <t>L1005</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1385,26 +1385,26 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>240</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46248</v>
+        <v>46223</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SMP-30106</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sample bracket 30106</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>L1029</t>
+          <t>L1081</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1418,21 +1418,21 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46220</v>
+        <v>46228</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30105</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30105</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>L1076</t>
+          <t>L1070</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1441,26 +1441,26 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46208</v>
+        <v>46293</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SMP-30108</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sample bracket 30108</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>L1018</t>
+          <t>L1088</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1474,21 +1474,21 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46219</v>
+        <v>46212</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SMP-30108</t>
+          <t>SMP-30101</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sample bracket 30108</t>
+          <t>Sample bracket 30101</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>L1014</t>
+          <t>L1074</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1497,12 +1497,12 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>50</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46305</v>
+        <v>46265</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>L1030</t>
+          <t>L1005</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1525,26 +1525,26 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46304</v>
+        <v>46199</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SMP-30110</t>
+          <t>SMP-30111</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sample bracket 30110</t>
+          <t>Sample bracket 30111</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>L1033</t>
+          <t>L1005</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1553,26 +1553,26 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46228</v>
+        <v>46236</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30106</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30106</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>L1067</t>
+          <t>L1085</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1586,21 +1586,21 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46260</v>
+        <v>46222</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SMP-30102</t>
+          <t>SMP-30111</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sample bracket 30102</t>
+          <t>Sample bracket 30111</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>L1099</t>
+          <t>L1052</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1609,26 +1609,26 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46262</v>
+        <v>46192</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SMP-30103</t>
+          <t>SMP-30104</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sample bracket 30103</t>
+          <t>Sample bracket 30104</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>L1028</t>
+          <t>L1030</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1637,26 +1637,26 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46230</v>
+        <v>46203</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SMP-30101</t>
+          <t>SMP-30105</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sample bracket 30101</t>
+          <t>Sample bracket 30105</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>L1084</t>
+          <t>L1003</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1665,26 +1665,26 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46262</v>
+        <v>46221</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>L1003</t>
+          <t>L1052</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1693,26 +1693,26 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46210</v>
+        <v>46289</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SMP-30115</t>
+          <t>SMP-30108</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sample bracket 30115</t>
+          <t>Sample bracket 30108</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>L1054</t>
+          <t>L1089</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1726,21 +1726,21 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46232</v>
+        <v>46205</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SMP-30115</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sample bracket 30115</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>L1056</t>
+          <t>L1060</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1749,26 +1749,26 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46275</v>
+        <v>46216</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SMP-30102</t>
+          <t>SMP-30106</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sample bracket 30102</t>
+          <t>Sample bracket 30106</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>L1018</t>
+          <t>L1058</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1777,26 +1777,26 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46279</v>
+        <v>46215</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30109</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30109</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>L1081</t>
+          <t>L1029</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1805,26 +1805,26 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46269</v>
+        <v>46239</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SMP-30110</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sample bracket 30110</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>L1076</t>
+          <t>L1051</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1833,26 +1833,26 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46262</v>
+        <v>46207</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30108</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30108</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>L1077</t>
+          <t>L1098</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1861,26 +1861,26 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46220</v>
+        <v>46241</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SMP-30103</t>
+          <t>SMP-30111</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sample bracket 30103</t>
+          <t>Sample bracket 30111</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>L1014</t>
+          <t>L1051</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1894,21 +1894,21 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46264</v>
+        <v>46188</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SMP-30106</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sample bracket 30106</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>L1029</t>
+          <t>L1014</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1917,26 +1917,26 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46214</v>
+        <v>46248</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SMP-30110</t>
+          <t>SMP-30105</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sample bracket 30110</t>
+          <t>Sample bracket 30105</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>L1051</t>
+          <t>L1033</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1945,12 +1945,12 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46276</v>
+        <v>46247</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>L1040</t>
+          <t>L1044</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1978,21 +1978,21 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46184</v>
+        <v>46245</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>L1087</t>
+          <t>L1065</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2001,26 +2001,26 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46294</v>
+        <v>46199</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SMP-30102</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sample bracket 30102</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>L1010</t>
+          <t>L1024</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2029,26 +2029,26 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46294</v>
+        <v>46232</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30101</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30101</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>L1094</t>
+          <t>L1000</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2057,26 +2057,26 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46251</v>
+        <v>46271</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30106</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30106</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>L1075</t>
+          <t>L1008</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2085,12 +2085,12 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>L1052</t>
+          <t>L1015</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2118,21 +2118,21 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46206</v>
+        <v>46238</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30109</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30109</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>L1092</t>
+          <t>L1041</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2141,12 +2141,12 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>L1045</t>
+          <t>L1024</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2169,26 +2169,26 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46289</v>
+        <v>46237</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SMP-30106</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sample bracket 30106</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>L1061</t>
+          <t>L1022</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2197,26 +2197,26 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46272</v>
+        <v>46267</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SMP-30103</t>
+          <t>SMP-30109</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sample bracket 30103</t>
+          <t>Sample bracket 30109</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>L1071</t>
+          <t>L1000</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2230,21 +2230,21 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46224</v>
+        <v>46285</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SMP-30103</t>
+          <t>SMP-30109</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sample bracket 30103</t>
+          <t>Sample bracket 30109</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>L1073</t>
+          <t>L1074</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2253,26 +2253,26 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46210</v>
+        <v>46261</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>L1098</t>
+          <t>L1056</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2281,26 +2281,26 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46245</v>
+        <v>46219</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SMP-30100</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sample bracket 30100</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>L1084</t>
+          <t>L1094</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2309,26 +2309,26 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46287</v>
+        <v>46278</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SMP-30100</t>
+          <t>SMP-30102</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sample bracket 30100</t>
+          <t>Sample bracket 30102</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>L1089</t>
+          <t>L1084</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2337,12 +2337,12 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46272</v>
+        <v>46294</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>L1023</t>
+          <t>L1096</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2370,21 +2370,21 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46297</v>
+        <v>46283</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SMP-30112</t>
+          <t>SMP-30109</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sample bracket 30112</t>
+          <t>Sample bracket 30109</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>L1094</t>
+          <t>L1025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2393,26 +2393,26 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46227</v>
+        <v>46299</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SMP-30102</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sample bracket 30102</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>L1027</t>
+          <t>L1060</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="72">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30102</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30102</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>L1020</t>
+          <t>L1080</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2449,26 +2449,26 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30106</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30106</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>L1099</t>
+          <t>L1049</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2477,26 +2477,26 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46203</v>
+        <v>46282</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SMP-30102</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sample bracket 30102</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>L1019</t>
+          <t>L1083</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2505,26 +2505,26 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46237</v>
+        <v>46222</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SMP-30101</t>
+          <t>SMP-30103</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sample bracket 30101</t>
+          <t>Sample bracket 30103</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>L1034</t>
+          <t>L1028</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2533,26 +2533,26 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46259</v>
+        <v>46299</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30114</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30114</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>L1056</t>
+          <t>L1031</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2561,26 +2561,26 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SMP-30108</t>
+          <t>SMP-30114</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sample bracket 30108</t>
+          <t>Sample bracket 30114</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>L1065</t>
+          <t>L1059</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2589,26 +2589,26 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>50</v>
+        <v>240</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46265</v>
+        <v>46185</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>L1036</t>
+          <t>L1056</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2622,21 +2622,21 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46254</v>
+        <v>46213</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SMP-30115</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sample bracket 30115</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>L1039</t>
+          <t>L1070</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2645,26 +2645,26 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46268</v>
+        <v>46227</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SMP-30107</t>
+          <t>SMP-30105</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sample bracket 30107</t>
+          <t>Sample bracket 30105</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>L1076</t>
+          <t>L1060</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2673,26 +2673,26 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46285</v>
+        <v>46226</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SMP-30100</t>
+          <t>SMP-30108</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sample bracket 30100</t>
+          <t>Sample bracket 30108</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>L1027</t>
+          <t>L1081</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2701,26 +2701,26 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46278</v>
+        <v>46243</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SMP-30108</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sample bracket 30108</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>L1015</t>
+          <t>L1035</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2729,26 +2729,26 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SMP-30115</t>
+          <t>SMP-30102</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sample bracket 30115</t>
+          <t>Sample bracket 30102</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>L1022</t>
+          <t>L1030</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2757,26 +2757,26 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46254</v>
+        <v>46275</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SMP-30112</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sample bracket 30112</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>L1029</t>
+          <t>L1069</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2785,26 +2785,26 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>240</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46296</v>
+        <v>46289</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30104</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30104</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>L1094</t>
+          <t>L1049</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2813,26 +2813,26 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30106</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30106</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>L1009</t>
+          <t>L1052</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2846,21 +2846,21 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46249</v>
+        <v>46266</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30114</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30114</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>L1090</t>
+          <t>L1026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2874,21 +2874,21 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46292</v>
+        <v>46198</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>L1002</t>
+          <t>L1074</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2897,26 +2897,26 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46218</v>
+        <v>46260</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SMP-30105</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sample bracket 30105</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>L1079</t>
+          <t>L1045</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2925,26 +2925,26 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46295</v>
+        <v>46209</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>L1013</t>
+          <t>L1053</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2953,26 +2953,26 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46247</v>
+        <v>46259</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30107</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30107</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>L1067</t>
+          <t>L1034</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2981,26 +2981,26 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46205</v>
+        <v>46302</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SMP-30112</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sample bracket 30112</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>L1095</t>
+          <t>L1043</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3009,26 +3009,26 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46274</v>
+        <v>46211</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SMP-30107</t>
+          <t>SMP-30105</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sample bracket 30107</t>
+          <t>Sample bracket 30105</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>L1021</t>
+          <t>L1016</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3037,26 +3037,26 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>50</v>
+        <v>240</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46254</v>
+        <v>46197</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SMP-30103</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sample bracket 30103</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>L1024</t>
+          <t>L1075</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3065,26 +3065,26 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46230</v>
+        <v>46295</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>L1082</t>
+          <t>L1054</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3098,21 +3098,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SMP-30107</t>
+          <t>SMP-30114</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sample bracket 30107</t>
+          <t>Sample bracket 30114</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>L1032</t>
+          <t>L1033</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3121,26 +3121,26 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46246</v>
+        <v>46284</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SMP-30105</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sample bracket 30105</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>L1097</t>
+          <t>L1041</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3149,26 +3149,26 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46185</v>
+        <v>46279</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SMP-30105</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sample bracket 30105</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>L1080</t>
+          <t>L1053</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3177,26 +3177,26 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46226</v>
+        <v>46260</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SMP-30114</t>
+          <t>SMP-30102</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sample bracket 30114</t>
+          <t>Sample bracket 30102</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>L1097</t>
+          <t>L1095</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3210,21 +3210,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46236</v>
+        <v>46153</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SMP-30114</t>
+          <t>SMP-30101</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sample bracket 30114</t>
+          <t>Sample bracket 30101</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>L1072</t>
+          <t>L1044</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3233,26 +3233,26 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46207</v>
+        <v>46222</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SMP-30110</t>
+          <t>SMP-30102</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sample bracket 30110</t>
+          <t>Sample bracket 30102</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>L1080</t>
+          <t>L1083</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3261,26 +3261,26 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46264</v>
+        <v>46185</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>L1060</t>
+          <t>L1025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3289,26 +3289,26 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46219</v>
+        <v>46282</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30104</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30104</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>L1075</t>
+          <t>L1060</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3322,21 +3322,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30106</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30106</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>L1039</t>
+          <t>L1032</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3345,26 +3345,26 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46301</v>
+        <v>46245</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SMP-30114</t>
+          <t>SMP-30105</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sample bracket 30114</t>
+          <t>Sample bracket 30105</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>L1047</t>
+          <t>L1095</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3373,26 +3373,26 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46241</v>
+        <v>46180</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SMP-30102</t>
+          <t>SMP-30105</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sample bracket 30102</t>
+          <t>Sample bracket 30105</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>L1011</t>
+          <t>L1013</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3406,21 +3406,21 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46261</v>
+        <v>46191</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SMP-30112</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sample bracket 30112</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>L1070</t>
+          <t>L1073</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3429,26 +3429,26 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46197</v>
+        <v>46188</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SMP-30114</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sample bracket 30114</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>L1073</t>
+          <t>L1025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3457,26 +3457,26 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46246</v>
+        <v>46293</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SMP-30110</t>
+          <t>SMP-30107</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sample bracket 30110</t>
+          <t>Sample bracket 30107</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>L1064</t>
+          <t>L1098</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3485,26 +3485,26 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46262</v>
+        <v>46219</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SMP-30101</t>
+          <t>SMP-30103</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sample bracket 30101</t>
+          <t>Sample bracket 30103</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>L1043</t>
+          <t>L1072</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3518,21 +3518,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46300</v>
+        <v>46254</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SMP-30105</t>
+          <t>SMP-30111</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sample bracket 30105</t>
+          <t>Sample bracket 30111</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>L1090</t>
+          <t>L1084</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3541,26 +3541,26 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SMP-30114</t>
+          <t>SMP-30102</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sample bracket 30114</t>
+          <t>Sample bracket 30102</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>L1078</t>
+          <t>L1043</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3569,26 +3569,26 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46270</v>
+        <v>46215</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>L1036</t>
+          <t>L1013</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3602,21 +3602,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46223</v>
+        <v>46242</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30111</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30111</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>L1086</t>
+          <t>L1058</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -3625,26 +3625,26 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46220</v>
+        <v>46287</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SMP-30101</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sample bracket 30101</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>L1082</t>
+          <t>L1066</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3658,21 +3658,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46274</v>
+        <v>46261</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SMP-30102</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Sample bracket 30102</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>L1071</t>
+          <t>L1093</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3681,26 +3681,26 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30108</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30108</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>L1084</t>
+          <t>L1031</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3709,26 +3709,26 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>240</v>
+        <v>50</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46274</v>
+        <v>46203</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30108</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30108</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>L1074</t>
+          <t>L1031</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -3737,26 +3737,26 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>L1083</t>
+          <t>L1063</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3765,26 +3765,26 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46247</v>
+        <v>46259</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30105</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30105</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>L1010</t>
+          <t>L1045</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3798,21 +3798,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46241</v>
+        <v>46279</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SMP-30112</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sample bracket 30112</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>L1042</t>
+          <t>L1076</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3821,26 +3821,26 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46241</v>
+        <v>46256</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SMP-30102</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sample bracket 30102</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>L1054</t>
+          <t>L1024</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3849,26 +3849,26 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>240</v>
+        <v>50</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46304</v>
+        <v>46231</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30107</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30107</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>L1039</t>
+          <t>L1062</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -3877,26 +3877,26 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46273</v>
+        <v>46235</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SMP-30106</t>
+          <t>SMP-30107</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sample bracket 30106</t>
+          <t>Sample bracket 30107</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>L1098</t>
+          <t>L1082</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3910,21 +3910,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46283</v>
+        <v>46220</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SMP-30106</t>
+          <t>SMP-30114</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sample bracket 30106</t>
+          <t>Sample bracket 30114</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>L1017</t>
+          <t>L1011</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -3933,26 +3933,26 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46277</v>
+        <v>46267</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SMP-30102</t>
+          <t>SMP-30107</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sample bracket 30102</t>
+          <t>Sample bracket 30107</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>L1012</t>
+          <t>L1031</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -3961,26 +3961,26 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46239</v>
+        <v>46260</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SMP-30101</t>
+          <t>SMP-30111</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sample bracket 30101</t>
+          <t>Sample bracket 30111</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>L1098</t>
+          <t>L1067</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -3989,26 +3989,26 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46246</v>
+        <v>46160</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>L1019</t>
+          <t>L1070</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4017,26 +4017,26 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46213</v>
+        <v>46233</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SMP-30105</t>
+          <t>SMP-30111</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Sample bracket 30105</t>
+          <t>Sample bracket 30111</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>L1098</t>
+          <t>L1034</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4045,26 +4045,26 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46231</v>
+        <v>46283</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SMP-30105</t>
+          <t>SMP-30108</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Sample bracket 30105</t>
+          <t>Sample bracket 30108</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>L1005</t>
+          <t>L1092</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4073,26 +4073,26 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46237</v>
+        <v>46292</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>L1030</t>
+          <t>L1068</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4101,26 +4101,26 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46226</v>
+        <v>46284</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30106</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30106</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>L1057</t>
+          <t>L1061</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4129,26 +4129,26 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46276</v>
+        <v>46172</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SMP-30107</t>
+          <t>SMP-30109</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Sample bracket 30107</t>
+          <t>Sample bracket 30109</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>L1060</t>
+          <t>L1024</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4157,26 +4157,26 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46236</v>
+        <v>46271</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30107</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30107</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>L1073</t>
+          <t>L1038</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4185,26 +4185,26 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46223</v>
+        <v>46279</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SMP-30114</t>
+          <t>SMP-30104</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Sample bracket 30114</t>
+          <t>Sample bracket 30104</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>L1099</t>
+          <t>L1006</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4213,26 +4213,26 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46179</v>
+        <v>46234</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30109</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30109</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>L1025</t>
+          <t>L1016</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
     </row>
     <row r="137">
@@ -4250,17 +4250,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30103</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30103</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>L1006</t>
+          <t>L1073</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4269,26 +4269,26 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46251</v>
+        <v>46260</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>L1013</t>
+          <t>L1043</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4297,26 +4297,26 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46278</v>
+        <v>46281</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SMP-30103</t>
+          <t>SMP-30101</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Sample bracket 30103</t>
+          <t>Sample bracket 30101</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>L1097</t>
+          <t>L1061</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4325,26 +4325,26 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46263</v>
+        <v>46267</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SMP-30108</t>
+          <t>SMP-30102</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Sample bracket 30108</t>
+          <t>Sample bracket 30102</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>L1065</t>
+          <t>L1009</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4353,26 +4353,26 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46294</v>
+        <v>46289</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30101</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30101</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>L1028</t>
+          <t>L1072</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4381,26 +4381,26 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46191</v>
+        <v>46163</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30102</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30102</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>L1053</t>
+          <t>L1015</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4409,26 +4409,26 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>50</v>
+        <v>240</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46257</v>
+        <v>46245</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SMP-30112</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Sample bracket 30112</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>L1030</t>
+          <t>L1079</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4437,26 +4437,26 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46270</v>
+        <v>46262</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SMP-30102</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Sample bracket 30102</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>L1003</t>
+          <t>L1056</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4470,21 +4470,21 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46212</v>
+        <v>46276</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SMP-30103</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Sample bracket 30103</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>L1083</t>
+          <t>L1079</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4493,26 +4493,26 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46290</v>
+        <v>46186</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30103</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30103</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>L1036</t>
+          <t>L1026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4521,26 +4521,26 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46225</v>
+        <v>46239</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30108</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30108</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>L1060</t>
+          <t>L1020</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -4549,26 +4549,26 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46197</v>
+        <v>46252</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SMP-30100</t>
+          <t>SMP-30105</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Sample bracket 30100</t>
+          <t>Sample bracket 30105</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>L1002</t>
+          <t>L1020</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4577,26 +4577,26 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46212</v>
+        <v>46262</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SMP-30106</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Sample bracket 30106</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>L1070</t>
+          <t>L1076</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46293</v>
+        <v>46301</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30109</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30109</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4633,26 +4633,26 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30114</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30114</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>L1030</t>
+          <t>L1029</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4661,26 +4661,26 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46297</v>
+        <v>46265</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SMP-30114</t>
+          <t>SMP-30106</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Sample bracket 30114</t>
+          <t>Sample bracket 30106</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>L1063</t>
+          <t>L1069</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4689,26 +4689,26 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46242</v>
+        <v>46197</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SMP-30100</t>
+          <t>SMP-30104</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Sample bracket 30100</t>
+          <t>Sample bracket 30104</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>L1073</t>
+          <t>L1018</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4717,26 +4717,26 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46277</v>
+        <v>46288</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30101</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30101</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>L1000</t>
+          <t>L1039</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4750,21 +4750,21 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30109</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30109</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>L1053</t>
+          <t>L1059</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4773,26 +4773,26 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46255</v>
+        <v>46187</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SMP-30102</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Sample bracket 30102</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>L1046</t>
+          <t>L1064</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4801,26 +4801,26 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>50</v>
+        <v>240</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46268</v>
+        <v>46264</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SMP-30100</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Sample bracket 30100</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>L1060</t>
+          <t>L1076</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4834,21 +4834,21 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46172</v>
+        <v>46229</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SMP-30112</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Sample bracket 30112</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>L1032</t>
+          <t>L1077</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -4857,26 +4857,26 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46220</v>
+        <v>46294</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>L1044</t>
+          <t>L1086</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -4885,26 +4885,26 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46223</v>
+        <v>46155</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SMP-30103</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Sample bracket 30103</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>L1094</t>
+          <t>L1086</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4918,21 +4918,21 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46300</v>
+        <v>46224</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30101</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30101</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>L1069</t>
+          <t>L1022</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -4941,26 +4941,26 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46213</v>
+        <v>46195</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SMP-30105</t>
+          <t>SMP-30114</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Sample bracket 30105</t>
+          <t>Sample bracket 30114</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>L1087</t>
+          <t>L1023</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="163">
@@ -4978,17 +4978,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SMP-30115</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Sample bracket 30115</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>L1017</t>
+          <t>L1062</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -5002,21 +5002,21 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46301</v>
+        <v>46272</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SMP-30114</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Sample bracket 30114</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>L1025</t>
+          <t>L1042</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5025,26 +5025,26 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46202</v>
+        <v>46208</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SMP-30106</t>
+          <t>SMP-30103</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Sample bracket 30106</t>
+          <t>Sample bracket 30103</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>L1040</t>
+          <t>L1042</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5053,26 +5053,26 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46167</v>
+        <v>46278</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SMP-30112</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Sample bracket 30112</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>L1069</t>
+          <t>L1051</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -5081,26 +5081,26 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46301</v>
+        <v>46262</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SMP-30108</t>
+          <t>SMP-30101</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Sample bracket 30108</t>
+          <t>Sample bracket 30101</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>L1082</t>
+          <t>L1040</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5109,26 +5109,26 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46272</v>
+        <v>46292</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>L1099</t>
+          <t>L1098</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5137,26 +5137,26 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46279</v>
+        <v>46239</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SMP-30110</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Sample bracket 30110</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>L1047</t>
+          <t>L1069</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5170,21 +5170,21 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46227</v>
+        <v>46298</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SMP-30112</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Sample bracket 30112</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>L1049</t>
+          <t>L1066</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5198,21 +5198,21 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46258</v>
+        <v>46243</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SMP-30105</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Sample bracket 30105</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>L1063</t>
+          <t>L1097</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5221,26 +5221,26 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46218</v>
+        <v>46280</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SMP-30108</t>
+          <t>SMP-30106</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Sample bracket 30108</t>
+          <t>Sample bracket 30106</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>L1093</t>
+          <t>L1016</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5249,26 +5249,26 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46264</v>
+        <v>46203</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SMP-30102</t>
+          <t>SMP-30114</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Sample bracket 30102</t>
+          <t>Sample bracket 30114</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>L1023</t>
+          <t>L1062</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5277,26 +5277,26 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>240</v>
+        <v>50</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46275</v>
+        <v>46176</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>L1010</t>
+          <t>L1077</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="175">
@@ -5314,17 +5314,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30105</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30105</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>L1077</t>
+          <t>L1001</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -5333,26 +5333,26 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46235</v>
+        <v>46294</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SMP-30105</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Sample bracket 30105</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>L1044</t>
+          <t>L1014</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -5366,21 +5366,21 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46230</v>
+        <v>46240</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SMP-30101</t>
+          <t>SMP-30103</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Sample bracket 30101</t>
+          <t>Sample bracket 30103</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>L1045</t>
+          <t>L1019</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -5389,26 +5389,26 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46279</v>
+        <v>46256</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30109</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30109</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>L1007</t>
+          <t>L1034</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -5417,26 +5417,26 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46271</v>
+        <v>46173</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SMP-30112</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Sample bracket 30112</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>L1095</t>
+          <t>L1031</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -5445,26 +5445,26 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46290</v>
+        <v>46269</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SMP-30100</t>
+          <t>SMP-30104</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Sample bracket 30100</t>
+          <t>Sample bracket 30104</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>L1077</t>
+          <t>L1076</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -5473,26 +5473,26 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46291</v>
+        <v>46207</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SMP-30101</t>
+          <t>SMP-30104</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sample bracket 30101</t>
+          <t>Sample bracket 30104</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>L1030</t>
+          <t>L1035</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -5501,26 +5501,26 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46269</v>
+        <v>46190</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>L1072</t>
+          <t>L1064</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -5529,26 +5529,26 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46236</v>
+        <v>46278</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>L1047</t>
+          <t>L1038</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -5557,26 +5557,26 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46224</v>
+        <v>46206</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SMP-30114</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Sample bracket 30114</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>L1073</t>
+          <t>L1057</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -5585,26 +5585,26 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>L1083</t>
+          <t>L1070</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -5613,26 +5613,26 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46181</v>
+        <v>46262</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SMP-30107</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Sample bracket 30107</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>L1003</t>
+          <t>L1041</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -5646,21 +5646,21 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46255</v>
+        <v>46249</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SMP-30115</t>
+          <t>SMP-30107</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Sample bracket 30115</t>
+          <t>Sample bracket 30107</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>L1071</t>
+          <t>L1029</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5669,26 +5669,26 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46222</v>
+        <v>46275</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SMP-30108</t>
+          <t>SMP-30101</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Sample bracket 30108</t>
+          <t>Sample bracket 30101</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>L1090</t>
+          <t>L1060</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5702,21 +5702,21 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SMP-30106</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Sample bracket 30106</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>L1036</t>
+          <t>L1083</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5725,26 +5725,26 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46292</v>
+        <v>46180</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SMP-30106</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Sample bracket 30106</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>L1009</t>
+          <t>L1016</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -5753,21 +5753,21 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SMP-30105</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Sample bracket 30105</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5786,21 +5786,21 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46238</v>
+        <v>46304</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SMP-30110</t>
+          <t>SMP-30114</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Sample bracket 30110</t>
+          <t>Sample bracket 30114</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>L1090</t>
+          <t>L1018</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -5809,26 +5809,26 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46201</v>
+        <v>46296</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30104</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30104</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>L1020</t>
+          <t>L1033</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -5837,26 +5837,26 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46256</v>
+        <v>46240</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>L1015</t>
+          <t>L1042</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -5865,26 +5865,26 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46282</v>
+        <v>46184</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>L1063</t>
+          <t>L1080</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -5893,26 +5893,26 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30101</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30101</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>L1047</t>
+          <t>L1030</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -5921,26 +5921,26 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46245</v>
+        <v>46227</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30107</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30107</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>L1011</t>
+          <t>L1055</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -5954,21 +5954,21 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46268</v>
+        <v>46263</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30103</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30103</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>L1091</t>
+          <t>L1088</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -5977,26 +5977,26 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46223</v>
+        <v>46299</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>L1073</t>
+          <t>L1007</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -6005,26 +6005,26 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46176</v>
+        <v>46270</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30111</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30111</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>L1082</t>
+          <t>L1018</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -6033,26 +6033,26 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46261</v>
+        <v>46250</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SMP-30114</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Sample bracket 30114</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>L1066</t>
+          <t>L1023</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6061,26 +6061,26 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46204</v>
+        <v>46296</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30105</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30105</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>L1099</t>
+          <t>L1048</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6094,21 +6094,21 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46224</v>
+        <v>46258</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SMP-30105</t>
+          <t>SMP-30107</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Sample bracket 30105</t>
+          <t>Sample bracket 30107</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>L1016</t>
+          <t>L1074</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -6117,26 +6117,26 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46213</v>
+        <v>46261</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SMP-30101</t>
+          <t>SMP-30107</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Sample bracket 30101</t>
+          <t>Sample bracket 30107</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>L1066</t>
+          <t>L1032</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -6145,26 +6145,26 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46288</v>
+        <v>46238</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30108</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30108</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>L1041</t>
+          <t>L1059</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -6173,26 +6173,26 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46186</v>
+        <v>46296</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30105</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30105</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>L1066</t>
+          <t>L1044</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -6201,26 +6201,26 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46281</v>
+        <v>46241</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SMP-30102</t>
+          <t>SMP-30109</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Sample bracket 30102</t>
+          <t>Sample bracket 30109</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>L1081</t>
+          <t>L1054</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -6229,26 +6229,26 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46291</v>
+        <v>46210</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SMP-30108</t>
+          <t>SMP-30114</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Sample bracket 30108</t>
+          <t>Sample bracket 30114</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>L1038</t>
+          <t>L1025</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -6257,26 +6257,26 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46257</v>
+        <v>46293</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SMP-30102</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Sample bracket 30102</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>L1021</t>
+          <t>L1048</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -6290,21 +6290,21 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46288</v>
+        <v>46249</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30111</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30111</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>L1079</t>
+          <t>L1089</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -6313,26 +6313,26 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46211</v>
+        <v>46174</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SMP-30110</t>
+          <t>SMP-30100</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Sample bracket 30110</t>
+          <t>Sample bracket 30100</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>L1072</t>
+          <t>L1084</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -6341,26 +6341,26 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46295</v>
+        <v>46306</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SMP-30100</t>
+          <t>SMP-30108</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Sample bracket 30100</t>
+          <t>Sample bracket 30108</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>L1082</t>
+          <t>L1087</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -6369,26 +6369,26 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>240</v>
+        <v>50</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46240</v>
+        <v>46213</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SMP-30108</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Sample bracket 30108</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>L1098</t>
+          <t>L1036</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -6397,26 +6397,26 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46244</v>
+        <v>46284</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30111</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30111</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>L1003</t>
+          <t>L1024</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -6425,26 +6425,26 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46241</v>
+        <v>46236</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>SMP-30109</t>
+          <t>SMP-30108</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Sample bracket 30109</t>
+          <t>Sample bracket 30108</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>L1038</t>
+          <t>L1092</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -6453,26 +6453,26 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46218</v>
+        <v>46198</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>SMP-30107</t>
+          <t>SMP-30103</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Sample bracket 30107</t>
+          <t>Sample bracket 30103</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>L1087</t>
+          <t>L1082</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -6481,12 +6481,12 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46262</v>
+        <v>46220</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>L1088</t>
+          <t>L1004</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -6509,26 +6509,26 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>50</v>
+        <v>240</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46264</v>
+        <v>46229</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>SMP-30105</t>
+          <t>SMP-30111</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Sample bracket 30105</t>
+          <t>Sample bracket 30111</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>L1061</t>
+          <t>L1011</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -6537,26 +6537,26 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46273</v>
+        <v>46227</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>SMP-30106</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Sample bracket 30106</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>L1018</t>
+          <t>L1022</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -6565,26 +6565,26 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46229</v>
+        <v>46221</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>SMP-30110</t>
+          <t>SMP-30104</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Sample bracket 30110</t>
+          <t>Sample bracket 30104</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>L1044</t>
+          <t>L1046</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -6593,26 +6593,26 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46225</v>
+        <v>46213</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30108</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30108</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>L1065</t>
+          <t>L1032</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -6621,26 +6621,26 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46275</v>
+        <v>46227</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SMP-30103</t>
+          <t>SMP-30109</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Sample bracket 30103</t>
+          <t>Sample bracket 30109</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>L1059</t>
+          <t>L1043</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -6654,16 +6654,16 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46263</v>
+        <v>46180</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SMP-30108</t>
+          <t>SMP-30114</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Sample bracket 30108</t>
+          <t>Sample bracket 30114</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6677,26 +6677,26 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46278</v>
+        <v>46179</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>SMP-30101</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Sample bracket 30101</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>L1049</t>
+          <t>L1071</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -6705,26 +6705,26 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46281</v>
+        <v>46220</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30102</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30102</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>L1020</t>
+          <t>L1001</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -6738,21 +6738,21 @@
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46286</v>
+        <v>46262</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>SMP-30110</t>
+          <t>SMP-30103</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Sample bracket 30110</t>
+          <t>Sample bracket 30103</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>L1020</t>
+          <t>L1086</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -6761,26 +6761,26 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46257</v>
+        <v>46215</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SMP-30114</t>
+          <t>SMP-30112</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Sample bracket 30114</t>
+          <t>Sample bracket 30112</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>L1039</t>
+          <t>L1047</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -6789,26 +6789,26 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46295</v>
+        <v>46260</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>SMP-30100</t>
+          <t>SMP-30107</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Sample bracket 30100</t>
+          <t>Sample bracket 30107</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>L1050</t>
+          <t>L1079</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -6822,21 +6822,21 @@
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46179</v>
+        <v>46195</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SMP-30114</t>
+          <t>SMP-30110</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Sample bracket 30114</t>
+          <t>Sample bracket 30110</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>L1027</t>
+          <t>L1028</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -6845,26 +6845,26 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>240</v>
+        <v>50</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46299</v>
+        <v>46197</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SMP-30111</t>
+          <t>SMP-30114</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Sample bracket 30111</t>
+          <t>Sample bracket 30114</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>L1036</t>
+          <t>L1038</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -6878,21 +6878,21 @@
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46278</v>
+        <v>46290</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SMP-30115</t>
+          <t>SMP-30103</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Sample bracket 30115</t>
+          <t>Sample bracket 30103</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>L1001</t>
+          <t>L1004</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -6901,26 +6901,26 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>SMP-30113</t>
+          <t>SMP-30115</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Sample bracket 30113</t>
+          <t>Sample bracket 30115</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>L1033</t>
+          <t>L1030</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -6929,26 +6929,26 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46271</v>
+        <v>46269</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SMP-30112</t>
+          <t>SMP-30104</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Sample bracket 30112</t>
+          <t>Sample bracket 30104</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>L1051</t>
+          <t>L1047</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -6957,26 +6957,26 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>50</v>
+        <v>240</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46271</v>
+        <v>46248</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>SMP-30106</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Sample bracket 30106</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>L1036</t>
+          <t>L1093</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -6985,26 +6985,26 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46257</v>
+        <v>46239</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>SMP-30112</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Sample bracket 30112</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>L1097</t>
+          <t>L1062</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -7018,21 +7018,21 @@
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46214</v>
+        <v>46188</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>SMP-30108</t>
+          <t>SMP-30113</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Sample bracket 30108</t>
+          <t>Sample bracket 30113</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>L1079</t>
+          <t>L1035</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -7041,26 +7041,26 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>240</v>
+        <v>50</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>SMP-30103</t>
+          <t>SMP-30111</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Sample bracket 30103</t>
+          <t>Sample bracket 30111</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>L1012</t>
+          <t>L1056</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -7069,12 +7069,12 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46219</v>
+        <v>46294</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>L1043</t>
+          <t>L1087</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -7097,12 +7097,12 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46226</v>
+        <v>46298</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>L1025</t>
+          <t>L1035</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -7125,26 +7125,26 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46257</v>
+        <v>46185</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>SMP-30112</t>
+          <t>SMP-30103</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Sample bracket 30112</t>
+          <t>Sample bracket 30103</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>L1005</t>
+          <t>L1058</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -7158,21 +7158,21 @@
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46232</v>
+        <v>46241</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>SMP-30104</t>
+          <t>SMP-30106</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Sample bracket 30104</t>
+          <t>Sample bracket 30106</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>L1060</t>
+          <t>L1076</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>240</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
